--- a/data/trans_camb/P1401-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P1401-Edad-trans_camb.xlsx
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-0,04</t>
+          <t>-0,05</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,18</t>
+          <t>0,19</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,06</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,17; -0,13</t>
+          <t>-1,2; -0,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 1,54</t>
+          <t>-0,71; 1,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,87</t>
+          <t>0,0; 0,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,91</t>
+          <t>0,0; 0,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,17</t>
+          <t>-0,52; 0,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 0,75</t>
+          <t>-0,31; 0,7</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-10,4%</t>
+          <t>-10,67%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-0,26</t>
+          <t>-0,34</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,54</t>
+          <t>-0,61</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,41</t>
+          <t>-0,48</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 0,01</t>
+          <t>-1,43; 0,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 0,75</t>
+          <t>-1,15; 0,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 1,43</t>
+          <t>-1,54; 1,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 0,57</t>
+          <t>-2,13; 0,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 0,43</t>
+          <t>-1,17; 0,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 0,35</t>
+          <t>-1,3; 0,2</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-34,73%</t>
+          <t>-45,15%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-37,76%</t>
+          <t>-42,31%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-37,03%</t>
+          <t>-43,61%</t>
         </is>
       </c>
     </row>
@@ -1024,27 +1024,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 397,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-68,69; 224,38</t>
+          <t>-72,07; 205,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-84,04; 87,33</t>
+          <t>-84,61; 67,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-72,6; 76,27</t>
+          <t>-72,59; 71,66</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-77,76; 57,31</t>
+          <t>-78,66; 55,79</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,19</t>
+          <t>0,52</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,73</t>
+          <t>-0,64</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,35</t>
+          <t>-0,04</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 1,24</t>
+          <t>-0,89; 1,26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 1,27</t>
+          <t>-0,59; 1,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 0,95</t>
+          <t>-3,2; 0,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 1,15</t>
+          <t>-2,79; 1,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 0,57</t>
+          <t>-1,63; 0,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 0,81</t>
+          <t>-1,15; 0,95</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-22,74%</t>
+          <t>-19,69%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-17,1%</t>
+          <t>-1,95%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-74,28; 396,79</t>
+          <t>-74,73; 398,64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-72,37; 337,46</t>
+          <t>-54,43; 577,4</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-69,08; 58,91</t>
+          <t>-70,94; 43,05</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-56,36; 62,33</t>
+          <t>-56,24; 51,18</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-62,12; 42,05</t>
+          <t>-60,02; 40,82</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-58,13; 60,25</t>
+          <t>-44,41; 64,4</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2,0</t>
+          <t>1,77</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-1,06</t>
+          <t>-1,09</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>0,31</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 0,76</t>
+          <t>-2,4; 0,75</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 3,94</t>
+          <t>-0,08; 3,67</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 0,55</t>
+          <t>-4,18; 0,79</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 0,94</t>
+          <t>-3,62; 1,04</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 0,17</t>
+          <t>-2,63; 0,36</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 1,91</t>
+          <t>-1,16; 1,94</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>118,46%</t>
+          <t>105,14%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-23,69%</t>
+          <t>-24,37%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-84,1; 111,23</t>
+          <t>-87,15; 111,37</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-11,37; 498,77</t>
+          <t>-11,37; 431,72</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-72,57; 24,44</t>
+          <t>-70,07; 35,25</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-54,53; 37,58</t>
+          <t>-55,19; 39,99</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-67,32; 10,41</t>
+          <t>-67,22; 19,16</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-29,19; 88,1</t>
+          <t>-29,1; 92,39</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0,6</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-0,28</t>
+          <t>1,29</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>1,01</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 0,43</t>
+          <t>-5,26; 0,68</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 3,24</t>
+          <t>-2,81; 3,58</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 4,61</t>
+          <t>-1,39; 4,47</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 2,06</t>
+          <t>-1,05; 3,67</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 1,8</t>
+          <t>-2,37; 1,92</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 1,82</t>
+          <t>-0,95; 2,73</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-8,38%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>29,07%</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-86,09; 52,96</t>
+          <t>-85,25; 60,31</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-47,19; 172,15</t>
+          <t>-46,62; 207,49</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-28,09; 281,98</t>
+          <t>-31,93; 215,35</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-74,92; 87,5</t>
+          <t>-24,61; 184,42</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-46,03; 78,07</t>
+          <t>-49,24; 81,73</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-51,23; 72,2</t>
+          <t>-22,06; 121,99</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3,86</t>
+          <t>4,15</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1,57</t>
+          <t>1,56</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,49</t>
+          <t>2,6</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 4,95</t>
+          <t>-1,67; 4,69</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,93; 7,18</t>
+          <t>0,7; 7,39</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 4,13</t>
+          <t>-1,35; 4,32</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 3,46</t>
+          <t>-0,75; 3,52</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 3,28</t>
+          <t>-0,75; 3,73</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,14</t>
+          <t>0,79; 4,31</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>132,66%</t>
+          <t>142,42%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>97,02%</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-39,06; 351,62</t>
+          <t>-40,74; 314,28</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>13,44; 524,97</t>
+          <t>8,54; 495,74</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-47,06; 289,04</t>
+          <t>-43,86; 273,85</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-21,19; 243,13</t>
+          <t>-24,3; 256,87</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-23,73; 185,5</t>
+          <t>-22,15; 204,5</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,62; 222,73</t>
+          <t>20,38; 255,38</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,97</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>0,12</t>
+          <t>0,26</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,48</t>
+          <t>0,61</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,24</t>
+          <t>-0,74; 0,22</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,49</t>
+          <t>0,36; 1,54</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,69</t>
+          <t>-0,76; 0,74</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 0,74</t>
+          <t>-0,38; 0,85</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 0,3</t>
+          <t>-0,57; 0,28</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,01; 0,92</t>
+          <t>0,22; 1,07</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>38,42%</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-52,97; 30,24</t>
+          <t>-51,9; 28,49</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>20,82; 175,9</t>
+          <t>24,85; 175,55</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-29,1; 41,74</t>
+          <t>-32,14; 45,22</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-25,1; 43,4</t>
+          <t>-16,43; 50,95</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-32,4; 22,78</t>
+          <t>-31,67; 21,13</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,41; 65,89</t>
+          <t>11,23; 79,32</t>
         </is>
       </c>
     </row>
